--- a/vat-knowledge/plants_abroad/Matrix_erweitert_EPDE.xlsx
+++ b/vat-knowledge/plants_abroad/Matrix_erweitert_EPDE.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Matrix_erweitert" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Hinweise" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MIRO_Eingang" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,7 +44,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -112,6 +118,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -587,68 +602,68 @@
           <t>Lagerauftrag Werk PL – WE Polen (Inland)</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr"/>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>PLxxx</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="O2" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -661,68 +676,68 @@
           <t>Lagerauftrag Werk PL – WE Italien (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr"/>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>ITxxx</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -735,68 +750,68 @@
           <t>Lagerauftrag Werk PL – WE Deutschland (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -809,68 +824,68 @@
           <t>Lagerauftrag Werk PL – WE Tschechien (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>CZxxx</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -883,68 +898,68 @@
           <t>Lagerauftrag Werk CZ – WE Tschechien (Inland)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>CZxxx</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>AE</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -957,68 +972,68 @@
           <t>Lagerauftrag Werk CZ – WE Slowakei (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>SKxxx</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="10" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -1031,68 +1046,68 @@
           <t>Lagerauftrag Werk CZ – WE Deutschland (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L8" s="10" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="O8" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -1105,68 +1120,68 @@
           <t>Lagerauftrag Werk DE – WE Deutschland (Inland)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="10" t="inlineStr">
         <is>
           <t>DS</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -1179,68 +1194,68 @@
           <t>Lagerauftrag Werk DE – WE Frankreich (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>FRxxx</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L10" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N10" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="O10" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -1253,68 +1268,68 @@
           <t>Strecke – Lieferant DE/EU (≠PL) – WE Polen</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>PLxxx</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" s="10" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1327,68 +1342,68 @@
           <t>Strecke – Lieferant DE/EU (≠CZ) – WE Tschechien</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr"/>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="9" t="inlineStr">
         <is>
           <t>CZxxx</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="10" t="inlineStr">
         <is>
           <t>AE</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N12" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O12" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1401,68 +1416,68 @@
           <t>Strecke – Lieferant DE/EU (≠SI) – WE Slowenien</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="9" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L13" s="10" t="inlineStr">
         <is>
           <t>CB</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="N13" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1475,68 +1490,68 @@
           <t>Strecke – Lieferant Schweden – WE Slowenien</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>CB</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1549,68 +1564,68 @@
           <t>Strecke – Lieferant DE/EU (≠BE) – WE Belgien</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>BE1022245089</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>BExxx</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1623,48 +1638,48 @@
           <t>Strecke – Lieferant DE/EU (≠NL) – WE Niederlande</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>NL827914052B01</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
         <is>
           <t>NLxxx</t>
         </is>
@@ -1674,17 +1689,17 @@
           <t>⚠ kein SAP-Stkz (Lücke)</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="M16" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="N16" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="O16" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1697,68 +1712,68 @@
           <t>Strecke – Lieferant DE/EU (≠LV) – WE Lettland</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>LV90013367396</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>LVxxx</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L17" s="10" t="inlineStr">
         <is>
           <t>LS</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="N17" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1771,68 +1786,68 @@
           <t>Strecke – Lieferant DE/EU (≠EE) – WE Estland</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr"/>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>EE102839441</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>EE</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>EE</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>EExxx</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L18" s="10" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="N18" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="O18" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1845,68 +1860,68 @@
           <t>Strecke – Lieferant Slowenien – WE Ungarn (Dreieck)</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>HUxxx</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L19" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="M19" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="N19" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1923,68 +1938,68 @@
           <t>Strecke – Lieferant Italien – WE Frankreich (Dreieck)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr"/>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>FRxxx</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L20" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
+      <c r="O20" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2001,68 +2016,68 @@
           <t>Strecke – Lieferant Polen – WE Spanien (Dreieck)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>ESxxx</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L21" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N21" s="3" t="inlineStr">
+      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2079,68 +2094,68 @@
           <t>Strecke – Lieferant Frankreich – WE Österreich (Dreieck)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>ATxxx</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L22" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="M22" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
+      <c r="N22" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
+      <c r="O22" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2157,68 +2172,68 @@
           <t>Strecke – Lieferant Tschechien – WE Rumänien (Dreieck)</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr"/>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>ROxxx</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L23" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="M23" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr">
+      <c r="N23" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2235,22 +2250,22 @@
           <t>Strecke EXW – Lieferant DE – WE Slowenien</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2260,47 +2275,47 @@
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L24" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M24" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr">
+      <c r="N24" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
+      <c r="O24" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2313,22 +2328,22 @@
           <t>Strecke EXW – Lieferant Slowenien (abgeholt) – WE Slowenien</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2338,47 +2353,47 @@
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L25" s="10" t="inlineStr">
         <is>
           <t>CB</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="M25" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N25" s="3" t="inlineStr">
+      <c r="N25" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="O25" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2391,22 +2406,22 @@
           <t>Strecke EXW – Lieferant Polen – WE Italien</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2416,47 +2431,47 @@
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>ITxxx</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="L26" s="10" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M26" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
+      <c r="N26" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
+      <c r="O26" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2469,22 +2484,22 @@
           <t>Strecke EXW – Lieferant Tschechien – WE Deutschland</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2494,47 +2509,47 @@
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="L27" s="10" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="M27" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="N27" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="O27" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2547,22 +2562,22 @@
           <t>Strecke EXW – Lieferant Belgien – WE Belgien (Inland)</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2572,47 +2587,47 @@
           <t>BE1022245089</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>BExxx</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="L28" s="10" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
+      <c r="M28" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N28" s="3" t="inlineStr">
+      <c r="N28" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
+      <c r="O28" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2625,22 +2640,22 @@
           <t>Strecke EXW – Lieferant Italien (ohne EPDE-UID) – WE Slowenien</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2650,47 +2665,47 @@
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K29" s="9" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="L29" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
+      <c r="M29" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N29" s="3" t="inlineStr">
+      <c r="N29" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="O29" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2707,22 +2722,22 @@
           <t>Strecke EXW – Lieferant Belgien – WE Frankreich (BE ig. Lief.)</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2732,27 +2747,27 @@
           <t>BE1022245089</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>FRxxx</t>
         </is>
@@ -2762,17 +2777,17 @@
           <t>⚠ kein SAP-Stkz (Lücke)</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N30" s="3" t="inlineStr">
+      <c r="N30" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
+      <c r="O30" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2785,22 +2800,22 @@
           <t>Strecke EXW – Lieferant Niederlande – WE Deutschland (NL ig. Lief.)</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2810,27 +2825,27 @@
           <t>NL827914052B01</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
@@ -2840,17 +2855,17 @@
           <t>⚠ kein SAP-Stkz (Lücke)</t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
+      <c r="M31" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N31" s="3" t="inlineStr">
+      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
+      <c r="O31" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2863,48 +2878,48 @@
           <t>Lagerauftrag Werk PL – WE Schweiz (Ausfuhr)</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr"/>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
         <is>
           <t>CHxxx</t>
         </is>
@@ -2914,17 +2929,17 @@
           <t>⚠ kein SAP-Stkz (Treatment fehlt: export)</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M32" s="9" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr">
+      <c r="N32" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
+      <c r="O32" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -2937,68 +2952,68 @@
           <t>Lager DE – WE Schweiz (Ausfuhr)</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr"/>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>CHxxx</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr">
+      <c r="L33" s="10" t="inlineStr">
         <is>
           <t>G0</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="M33" s="9" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
+      <c r="O33" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -3011,68 +3026,68 @@
           <t>Lager DE – WE Liechtenstein (Ausfuhr, Schweizer MWST-Raum)</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr"/>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>LI</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>LIxxx</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr">
+      <c r="L34" s="10" t="inlineStr">
         <is>
           <t>G0</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
+      <c r="M34" s="9" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N34" s="3" t="inlineStr">
+      <c r="N34" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
+      <c r="O34" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -3085,68 +3100,68 @@
           <t>Lager DE – WE Großbritannien (Ausfuhr, Post-Brexit)</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr"/>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>GBxxx</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="L35" s="10" t="inlineStr">
         <is>
           <t>G0</t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr">
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N35" s="3" t="inlineStr">
+      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
+      <c r="O35" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -3159,68 +3174,68 @@
           <t>Strecke – Lieferant DE/EU – WE Großbritannien (Ausfuhr)</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr"/>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K36" s="9" t="inlineStr">
         <is>
           <t>GBxxx</t>
         </is>
       </c>
-      <c r="L36" s="4" t="inlineStr">
+      <c r="L36" s="10" t="inlineStr">
         <is>
           <t>G0</t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr">
+      <c r="M36" s="9" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N36" s="3" t="inlineStr">
+      <c r="N36" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
+      <c r="O36" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -3237,48 +3252,48 @@
           <t>Lager PL-Werk – WE Großbritannien (Ausfuhr) [Lücke: kein PL-Export-Stkz]</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr"/>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K37" s="9" t="inlineStr">
         <is>
           <t>GBxxx</t>
         </is>
@@ -3288,17 +3303,17 @@
           <t>⚠ kein SAP-Stkz (Treatment fehlt: export)</t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr">
+      <c r="M37" s="9" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N37" s="3" t="inlineStr">
+      <c r="N37" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
+      <c r="O37" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -3311,22 +3326,22 @@
           <t>Strecke EXW – Lieferant Slowenien – WE Italien (SI ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -3336,47 +3351,47 @@
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K38" s="9" t="inlineStr">
         <is>
           <t>ITxxx</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr">
+      <c r="L38" s="10" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr">
+      <c r="M38" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N38" s="3" t="inlineStr">
+      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
+      <c r="O38" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -3389,22 +3404,22 @@
           <t>Strecke EXW – Lieferant Slowenien – WE Deutschland (SI ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -3414,47 +3429,47 @@
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L39" s="4" t="inlineStr">
+      <c r="L39" s="10" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="M39" s="3" t="inlineStr">
+      <c r="M39" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N39" s="3" t="inlineStr">
+      <c r="N39" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
+      <c r="O39" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -3467,68 +3482,68 @@
           <t>Dreieck – Lieferant Frankreich → EPDE(DE) → WE Italien (Art. 141)</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr"/>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" s="9" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="K40" s="9" t="inlineStr">
         <is>
           <t>ITxxx</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="L40" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="M40" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N40" s="3" t="inlineStr">
+      <c r="N40" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
+      <c r="O40" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -3545,68 +3560,68 @@
           <t>Dreieck – Lieferant Italien → EPDE(DE) → WE Spanien (Art. 141)</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr"/>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" s="9" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
+      <c r="K41" s="9" t="inlineStr">
         <is>
           <t>ESxxx</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="L41" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr">
+      <c r="M41" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N41" s="3" t="inlineStr">
+      <c r="N41" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
+      <c r="O41" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -3628,7 +3643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3707,6 +3722,1160 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>MIRO-Eingangsblatt</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Zweites Prinzip: die Eingangs-/Vorsteuerseite (MIRO). Blatt „MIRO_Eingang" leitet je Einkaufsfall das erwartete Eingangs-Kennzeichen ab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>MIRO — 4 Vorgänge</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>1) ig. Erwerb (eingehende Lieferung BEWEGT → Ankunftsland, Selbstveranlagung VE/VH/W5/EC/UR/BP/EP/LP/NP/IP, netto 0). 2) Inlandseinkauf (eingehende Lieferung RUHEND → Lieferant weist lokale MwSt aus, Vorsteuer VD/V2/B7/…). 3) Reverse Charge (DE §13b→DC, AT→RC, IT→VI). 4) Einfuhr Drittland (EUSt über EORI, kein Tabellen-MWSKZ). Sonderfall: eigene Ware ab Werk = kein Vorsteuervorgang (not relevant).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>MIRO — zwei Zusatz-Eingaben</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Anders als die Verkaufsseite braucht MIRO: (a) das LIEFERANTENLAND und (b) ob die EINGEHENDE Lieferung BEWEGT oder RUHEND ist. Genau das entscheidet zwischen ig. Erwerb (z. B. W5) und Inlandseinkauf (z. B. B7) — dieselbe Transportzuordnungs-Abhängigkeit wie oben.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>MIRO — offene Klärung</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Der Workshop hat MIRO als teils MANUELL markiert („steuerliches Abgangsland in der MIRO-Buchung korrekt pflegen"). Vor Automatisierung mit dem SAP-Team klären, ob die Findung MIRO automatisch ermitteln soll oder ob es ein manuell gepflegter Schritt bleibt.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Einkaufsfall</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>BUKRS</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Lieferantenland</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>eingehende Lieferung</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Waren-/Ankunftsland</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Erwerber-UID (BUKRS)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tax code Miro</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Vorgang (Info)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Hinweis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant FR → Ware nach DE</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>bewegt</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>DE449663039</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>VH</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>ig. Erwerb (Selbstveranlagung)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Vorlieferung grenzüberschreitend zu uns → ig. Erwerb DE (VH), netto 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant DE → Ware nach PL (wir PL-registriert)</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>bewegt</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>PL5263841834</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>ig. Erwerb (Selbstveranlagung)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>ig. Erwerb im Ankunftsland PL über PL-UID</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant AT → Ware nach SI</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>bewegt</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>SI66423562</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>ig. Erwerb (Selbstveranlagung)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>ig. Erwerb SI (EC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant SK → Ware nach CZ</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>bewegt</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>CZ687387072</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>ig. Erwerb (Selbstveranlagung)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>ig. Erwerb CZ (UR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant FR → Ware nach BE</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>bewegt</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>BE1022245089</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>BP</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>ig. Erwerb (Selbstveranlagung)</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>ig. Erwerb BE (BP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant DE → Ware nach NL</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>bewegt</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>NL827914052B01</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>NP</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>ig. Erwerb (Selbstveranlagung)</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>ig. Erwerb NL (NP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant DE → Ware nach EE</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>bewegt</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>EE102839441</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>ig. Erwerb (Selbstveranlagung)</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>ig. Erwerb EE (EP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant DE → Ware nach LV</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>bewegt</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>LV90013367396</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>ig. Erwerb (Selbstveranlagung)</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>ig. Erwerb LV (LP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant FR → Ware nach IT</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>bewegt</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>ig. Erwerb (Selbstveranlagung)</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>ig. Erwerb IT (IP) – nur bei IT-Registrierung</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant PL → PL-Inlandslieferung an uns</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>ruhend</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>PL5263841834</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Inlandseinkauf (Vorsteuer)</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Ware schon in PL, Lieferant weist 23% PL-MwSt aus → Vorsteuer B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant DE → DE-Inlandslieferung an uns</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>ruhend</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>DE449663039</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>VD</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Inlandseinkauf (Vorsteuer)</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>19% DE-Vorsteuer VD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant SI → SI-Inlandslieferung an uns</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ruhend</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>SI66423562</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Inlandseinkauf (Vorsteuer)</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22% SI-Vorsteuer</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant CZ → CZ-Inlandslieferung an uns</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>ruhend</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>CZ687387072</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>VC</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Inlandseinkauf (Vorsteuer)</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21% CZ-Vorsteuer VC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant BE → BE-Inlandslieferung an uns</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>ruhend</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>BE1022245089</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Inlandseinkauf (Vorsteuer)</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>21% BE-Vorsteuer BI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant NL → NL-Inlandslieferung an uns</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>ruhend</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>NL827914052B01</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>NI</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Inlandseinkauf (Vorsteuer)</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21% NL-Vorsteuer NI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant IT → IT-Inlandslieferung an uns</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>ruhend</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Inlandseinkauf (Vorsteuer)</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>22% IT-Vorsteuer VI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>DE Werklieferung/Leistung (§ 13b UStG)</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>ruhend</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>DE449663039</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>Reverse Charge</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>§13b: Leistungsempfänger schuldet Steuer → DC (nicht bei reiner Warenlieferung)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>IT Inland mit Reverse Charge (inversione)</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>ruhend</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Reverse Charge</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>IT-Inlands-RC → Eingang VI (nur mit IT-UID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant CH → Einfuhr nach DE</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Einfuhr</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>EORI (keine UID)</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>EUSt / EORI (kein MWSKZ)</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Einfuhr Drittland</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Einfuhrumsatzsteuer über EORI, als Vorsteuer abziehbar – kein Tabellen-MWSKZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant GB → Einfuhr nach DE</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Einfuhr</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>EORI (keine UID)</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>EUSt / EORI (kein MWSKZ)</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Einfuhr Drittland</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>EUSt über EORI (Post-Brexit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Eigene Ware ab Werk DE (Lagerauftrag)</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>entfällt</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>not relevant</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>kein Vorsteuervorgang</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Verkauf eigener Ware ab Werk → kein Einkaufs-/Vorsteuervorgang</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Eigene Ware ab Werk PL (Lagerauftrag)</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>entfällt</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>not relevant</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>kein Vorsteuervorgang</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>kein Vorsteuervorgang</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vat-knowledge/plants_abroad/Matrix_erweitert_EPDE.xlsx
+++ b/vat-knowledge/plants_abroad/Matrix_erweitert_EPDE.xlsx
@@ -602,68 +602,68 @@
           <t>Lagerauftrag Werk PL – WE Polen (Inland)</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>PLxxx</t>
         </is>
       </c>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N2" s="9" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O2" s="9" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -676,68 +676,68 @@
           <t>Lagerauftrag Werk PL – WE Italien (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>ITxxx</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O3" s="9" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -750,68 +750,68 @@
           <t>Lagerauftrag Werk PL – WE Deutschland (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N4" s="9" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -824,68 +824,68 @@
           <t>Lagerauftrag Werk PL – WE Tschechien (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>CZxxx</t>
         </is>
       </c>
-      <c r="L5" s="10" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O5" s="9" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -898,68 +898,68 @@
           <t>Lagerauftrag Werk CZ – WE Tschechien (Inland)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>CZxxx</t>
         </is>
       </c>
-      <c r="L6" s="10" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>AE</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N6" s="9" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O6" s="9" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -972,68 +972,68 @@
           <t>Lagerauftrag Werk CZ – WE Slowakei (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>SKxxx</t>
         </is>
       </c>
-      <c r="L7" s="10" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N7" s="9" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -1046,68 +1046,68 @@
           <t>Lagerauftrag Werk CZ – WE Deutschland (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L8" s="10" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N8" s="9" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O8" s="9" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -1120,68 +1120,68 @@
           <t>Lagerauftrag Werk DE – WE Deutschland (Inland)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L9" s="10" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>DS</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N9" s="9" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O9" s="9" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -1194,68 +1194,68 @@
           <t>Lagerauftrag Werk DE – WE Frankreich (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>FRxxx</t>
         </is>
       </c>
-      <c r="L10" s="10" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N10" s="9" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -1268,68 +1268,68 @@
           <t>Strecke – Lieferant DE/EU (≠PL) – WE Polen</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>PLxxx</t>
         </is>
       </c>
-      <c r="L11" s="10" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="M11" s="9" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N11" s="9" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O11" s="9" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1342,68 +1342,68 @@
           <t>Strecke – Lieferant DE/EU (≠CZ) – WE Tschechien</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>CZxxx</t>
         </is>
       </c>
-      <c r="L12" s="10" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>AE</t>
         </is>
       </c>
-      <c r="M12" s="9" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N12" s="9" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O12" s="9" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1416,68 +1416,68 @@
           <t>Strecke – Lieferant DE/EU (≠SI) – WE Slowenien</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L13" s="10" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>CB</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N13" s="9" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1490,68 +1490,68 @@
           <t>Strecke – Lieferant Schweden – WE Slowenien</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>CB</t>
         </is>
       </c>
-      <c r="M14" s="9" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N14" s="9" t="inlineStr">
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O14" s="9" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1564,68 +1564,68 @@
           <t>Strecke – Lieferant DE/EU (≠BE) – WE Belgien</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>BE1022245089</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>BExxx</t>
         </is>
       </c>
-      <c r="L15" s="10" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1638,48 +1638,48 @@
           <t>Strecke – Lieferant DE/EU (≠NL) – WE Niederlande</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>NL827914052B01</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>NLxxx</t>
         </is>
@@ -1689,17 +1689,17 @@
           <t>⚠ kein SAP-Stkz (Lücke)</t>
         </is>
       </c>
-      <c r="M16" s="9" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N16" s="9" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O16" s="9" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1712,68 +1712,68 @@
           <t>Strecke – Lieferant DE/EU (≠LV) – WE Lettland</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>LV90013367396</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>LVxxx</t>
         </is>
       </c>
-      <c r="L17" s="10" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>LS</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N17" s="9" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O17" s="9" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1786,68 +1786,68 @@
           <t>Strecke – Lieferant DE/EU (≠EE) – WE Estland</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>EE102839441</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>EE</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>EE</t>
         </is>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>EExxx</t>
         </is>
       </c>
-      <c r="L18" s="10" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="M18" s="9" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N18" s="9" t="inlineStr">
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O18" s="9" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1860,75 +1860,75 @@
           <t>Strecke – Lieferant Slowenien – WE Ungarn (Dreieck)</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>HUxxx</t>
         </is>
       </c>
-      <c r="L19" s="10" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M19" s="9" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N19" s="9" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O19" s="9" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck)</t>
+          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck, Art. 141)</t>
         </is>
       </c>
     </row>
@@ -1938,75 +1938,75 @@
           <t>Strecke – Lieferant Italien – WE Frankreich (Dreieck)</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>FRxxx</t>
         </is>
       </c>
-      <c r="L20" s="10" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N20" s="9" t="inlineStr">
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O20" s="9" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck)</t>
+          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck, Art. 141)</t>
         </is>
       </c>
     </row>
@@ -2016,75 +2016,75 @@
           <t>Strecke – Lieferant Polen – WE Spanien (Dreieck)</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>ESxxx</t>
         </is>
       </c>
-      <c r="L21" s="10" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O21" s="9" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck)</t>
+          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck, Art. 141)</t>
         </is>
       </c>
     </row>
@@ -2094,75 +2094,75 @@
           <t>Strecke – Lieferant Frankreich – WE Österreich (Dreieck)</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>ATxxx</t>
         </is>
       </c>
-      <c r="L22" s="10" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N22" s="9" t="inlineStr">
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O22" s="9" t="inlineStr">
+      <c r="O22" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck)</t>
+          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck, Art. 141)</t>
         </is>
       </c>
     </row>
@@ -2172,75 +2172,75 @@
           <t>Strecke – Lieferant Tschechien – WE Rumänien (Dreieck)</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>ROxxx</t>
         </is>
       </c>
-      <c r="L23" s="10" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N23" s="9" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O23" s="9" t="inlineStr">
+      <c r="O23" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck)</t>
+          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck, Art. 141)</t>
         </is>
       </c>
     </row>
@@ -2250,22 +2250,22 @@
           <t>Strecke EXW – Lieferant DE – WE Slowenien</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2275,47 +2275,47 @@
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L24" s="10" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N24" s="9" t="inlineStr">
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O24" s="9" t="inlineStr">
+      <c r="O24" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2328,22 +2328,22 @@
           <t>Strecke EXW – Lieferant Slowenien (abgeholt) – WE Slowenien</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2353,47 +2353,47 @@
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L25" s="10" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>CB</t>
         </is>
       </c>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N25" s="9" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O25" s="9" t="inlineStr">
+      <c r="O25" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2406,22 +2406,22 @@
           <t>Strecke EXW – Lieferant Polen – WE Italien</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2431,47 +2431,47 @@
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>ITxxx</t>
         </is>
       </c>
-      <c r="L26" s="10" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N26" s="9" t="inlineStr">
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O26" s="9" t="inlineStr">
+      <c r="O26" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2484,22 +2484,22 @@
           <t>Strecke EXW – Lieferant Tschechien – WE Deutschland</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2509,47 +2509,47 @@
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L27" s="10" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="M27" s="9" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N27" s="9" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O27" s="9" t="inlineStr">
+      <c r="O27" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2562,22 +2562,22 @@
           <t>Strecke EXW – Lieferant Belgien – WE Belgien (Inland)</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2587,47 +2587,47 @@
           <t>BE1022245089</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>BExxx</t>
         </is>
       </c>
-      <c r="L28" s="10" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N28" s="9" t="inlineStr">
+      <c r="N28" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O28" s="9" t="inlineStr">
+      <c r="O28" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2640,22 +2640,22 @@
           <t>Strecke EXW – Lieferant Italien (ohne EPDE-UID) – WE Slowenien</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2665,47 +2665,47 @@
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>EXW: Lieferantland -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L29" s="10" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M29" s="9" t="inlineStr">
+      <c r="M29" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N29" s="9" t="inlineStr">
+      <c r="N29" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O29" s="9" t="inlineStr">
+      <c r="O29" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2722,22 +2722,22 @@
           <t>Strecke EXW – Lieferant Belgien – WE Frankreich (BE ig. Lief.)</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2747,27 +2747,27 @@
           <t>BE1022245089</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>FRxxx</t>
         </is>
@@ -2777,17 +2777,17 @@
           <t>⚠ kein SAP-Stkz (Lücke)</t>
         </is>
       </c>
-      <c r="M30" s="9" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N30" s="9" t="inlineStr">
+      <c r="N30" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O30" s="9" t="inlineStr">
+      <c r="O30" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2800,22 +2800,22 @@
           <t>Strecke EXW – Lieferant Niederlande – WE Deutschland (NL ig. Lief.)</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2825,27 +2825,27 @@
           <t>NL827914052B01</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
@@ -2855,17 +2855,17 @@
           <t>⚠ kein SAP-Stkz (Lücke)</t>
         </is>
       </c>
-      <c r="M31" s="9" t="inlineStr">
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N31" s="9" t="inlineStr">
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O31" s="9" t="inlineStr">
+      <c r="O31" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2878,48 +2878,48 @@
           <t>Lagerauftrag Werk PL – WE Schweiz (Ausfuhr)</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr"/>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>CHxxx</t>
         </is>
@@ -2929,17 +2929,17 @@
           <t>⚠ kein SAP-Stkz (Treatment fehlt: export)</t>
         </is>
       </c>
-      <c r="M32" s="9" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N32" s="9" t="inlineStr">
+      <c r="N32" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O32" s="9" t="inlineStr">
+      <c r="O32" s="3" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -2952,68 +2952,68 @@
           <t>Lager DE – WE Schweiz (Ausfuhr)</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr"/>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>CHxxx</t>
         </is>
       </c>
-      <c r="L33" s="10" t="inlineStr">
+      <c r="L33" s="4" t="inlineStr">
         <is>
           <t>G0</t>
         </is>
       </c>
-      <c r="M33" s="9" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N33" s="9" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O33" s="9" t="inlineStr">
+      <c r="O33" s="3" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -3026,68 +3026,68 @@
           <t>Lager DE – WE Liechtenstein (Ausfuhr, Schweizer MWST-Raum)</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr"/>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>LI</t>
         </is>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>LIxxx</t>
         </is>
       </c>
-      <c r="L34" s="10" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr">
         <is>
           <t>G0</t>
         </is>
       </c>
-      <c r="M34" s="9" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N34" s="9" t="inlineStr">
+      <c r="N34" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O34" s="9" t="inlineStr">
+      <c r="O34" s="3" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -3100,68 +3100,68 @@
           <t>Lager DE – WE Großbritannien (Ausfuhr, Post-Brexit)</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr"/>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>GBxxx</t>
         </is>
       </c>
-      <c r="L35" s="10" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>G0</t>
         </is>
       </c>
-      <c r="M35" s="9" t="inlineStr">
+      <c r="M35" s="3" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N35" s="9" t="inlineStr">
+      <c r="N35" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O35" s="9" t="inlineStr">
+      <c r="O35" s="3" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -3174,75 +3174,75 @@
           <t>Strecke – Lieferant DE/EU – WE Großbritannien (Ausfuhr)</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr"/>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>GBxxx</t>
         </is>
       </c>
-      <c r="L36" s="10" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr">
         <is>
           <t>G0</t>
         </is>
       </c>
-      <c r="M36" s="9" t="inlineStr">
+      <c r="M36" s="3" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N36" s="9" t="inlineStr">
+      <c r="N36" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O36" s="9" t="inlineStr">
+      <c r="O36" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck)</t>
+          <t>Drittland-Ausfuhr über Heimat-UID (DE); KEIN Dreieck</t>
         </is>
       </c>
     </row>
@@ -3252,48 +3252,48 @@
           <t>Lager PL-Werk – WE Großbritannien (Ausfuhr) [Lücke: kein PL-Export-Stkz]</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>GBxxx</t>
         </is>
@@ -3303,17 +3303,17 @@
           <t>⚠ kein SAP-Stkz (Treatment fehlt: export)</t>
         </is>
       </c>
-      <c r="M37" s="9" t="inlineStr">
+      <c r="M37" s="3" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N37" s="9" t="inlineStr">
+      <c r="N37" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O37" s="9" t="inlineStr">
+      <c r="O37" s="3" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -3326,22 +3326,22 @@
           <t>Strecke EXW – Lieferant Slowenien – WE Italien (SI ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -3351,47 +3351,47 @@
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J38" s="9" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>ITxxx</t>
         </is>
       </c>
-      <c r="L38" s="10" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="M38" s="9" t="inlineStr">
+      <c r="M38" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N38" s="9" t="inlineStr">
+      <c r="N38" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O38" s="9" t="inlineStr">
+      <c r="O38" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -3404,22 +3404,22 @@
           <t>Strecke EXW – Lieferant Slowenien – WE Deutschland (SI ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -3429,47 +3429,47 @@
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K39" s="9" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L39" s="10" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="M39" s="9" t="inlineStr">
+      <c r="M39" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N39" s="9" t="inlineStr">
+      <c r="N39" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O39" s="9" t="inlineStr">
+      <c r="O39" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -3482,75 +3482,75 @@
           <t>Dreieck – Lieferant Frankreich → EPDE(DE) → WE Italien (Art. 141)</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr"/>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>ITxxx</t>
         </is>
       </c>
-      <c r="L40" s="10" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M40" s="9" t="inlineStr">
+      <c r="M40" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N40" s="9" t="inlineStr">
+      <c r="N40" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O40" s="9" t="inlineStr">
+      <c r="O40" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck)</t>
+          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck, Art. 141)</t>
         </is>
       </c>
     </row>
@@ -3560,75 +3560,75 @@
           <t>Dreieck – Lieferant Italien → EPDE(DE) → WE Spanien (Art. 141)</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr"/>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="K41" s="3" t="inlineStr">
         <is>
           <t>ESxxx</t>
         </is>
       </c>
-      <c r="L41" s="10" t="inlineStr">
+      <c r="L41" s="4" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M41" s="9" t="inlineStr">
+      <c r="M41" s="3" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N41" s="9" t="inlineStr">
+      <c r="N41" s="3" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O41" s="9" t="inlineStr">
+      <c r="O41" s="3" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck)</t>
+          <t>Ship-to ohne EPDE-UID -&gt; BUKRS DE (Dreieck, Art. 141)</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3719,54 +3719,6 @@
       <c r="B6" s="8" t="inlineStr">
         <is>
           <t>WICHTIG: Diese Matrix bildet die SAP-Findung ab, die ship-to-/werks-/incoterm-basiert ist. Im EU-Reihengeschäft kann DIESELBE Länderkonstellation je nachdem, WER die Ware transportiert (Lieferant / mittlerer Unternehmer / Kunde) und an WELCHER Position der eigene Buchungskreis in der Kette steht (erster / mittlerer / letzter), eine ANDERE bewegte Lieferung und damit ein ANDERES Kennzeichen ergeben (EuGH C-245/04 EMAG; Art. 36a MwStSystRL / Quick Fixes). Die SAP-Findung modelliert diese Transportzuordnung nach aktuellem Stand NICHT explizit — sie leitet aus Werk/Ship-to/Incoterm ab. EXW ist der EINZIGE explizit abgebildete Transport-Trigger. Bei mehrgliedrigen Ketten mit abweichender Transportveranlassung daher gesondert prüfen: hier besteht zwischen der ship-to-basierten SAP-Logik und der transportbasierten Rechtslage eine bewusste Vereinfachung. Mit dem SAP-Team klären, ob die Findung Transportzuordnung überhaupt berücksichtigen soll.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>MIRO-Eingangsblatt</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Zweites Prinzip: die Eingangs-/Vorsteuerseite (MIRO). Blatt „MIRO_Eingang" leitet je Einkaufsfall das erwartete Eingangs-Kennzeichen ab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>MIRO — 4 Vorgänge</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>1) ig. Erwerb (eingehende Lieferung BEWEGT → Ankunftsland, Selbstveranlagung VE/VH/W5/EC/UR/BP/EP/LP/NP/IP, netto 0). 2) Inlandseinkauf (eingehende Lieferung RUHEND → Lieferant weist lokale MwSt aus, Vorsteuer VD/V2/B7/…). 3) Reverse Charge (DE §13b→DC, AT→RC, IT→VI). 4) Einfuhr Drittland (EUSt über EORI, kein Tabellen-MWSKZ). Sonderfall: eigene Ware ab Werk = kein Vorsteuervorgang (not relevant).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>MIRO — zwei Zusatz-Eingaben</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Anders als die Verkaufsseite braucht MIRO: (a) das LIEFERANTENLAND und (b) ob die EINGEHENDE Lieferung BEWEGT oder RUHEND ist. Genau das entscheidet zwischen ig. Erwerb (z. B. W5) und Inlandseinkauf (z. B. B7) — dieselbe Transportzuordnungs-Abhängigkeit wie oben.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>MIRO — offene Klärung</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Der Workshop hat MIRO als teils MANUELL markiert („steuerliches Abgangsland in der MIRO-Buchung korrekt pflegen"). Vor Automatisierung mit dem SAP-Team klären, ob die Findung MIRO automatisch ermitteln soll oder ob es ein manuell gepflegter Schritt bleibt.</t>
         </is>
       </c>
     </row>

--- a/vat-knowledge/plants_abroad/Matrix_erweitert_EPDE.xlsx
+++ b/vat-knowledge/plants_abroad/Matrix_erweitert_EPDE.xlsx
@@ -602,68 +602,68 @@
           <t>Lagerauftrag Werk PL – WE Polen (Inland)</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr"/>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>PLxxx</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="O2" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -676,68 +676,68 @@
           <t>Lagerauftrag Werk PL – WE Italien (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr"/>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>ITxxx</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -750,68 +750,68 @@
           <t>Lagerauftrag Werk PL – WE Deutschland (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -824,68 +824,68 @@
           <t>Lagerauftrag Werk PL – WE Tschechien (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>CZxxx</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -898,68 +898,68 @@
           <t>Lagerauftrag Werk CZ – WE Tschechien (Inland)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>CZxxx</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>AE</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -972,68 +972,68 @@
           <t>Lagerauftrag Werk CZ – WE Slowakei (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>SKxxx</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="10" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -1046,68 +1046,68 @@
           <t>Lagerauftrag Werk CZ – WE Deutschland (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>1703</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L8" s="10" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="O8" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -1120,68 +1120,68 @@
           <t>Lagerauftrag Werk DE – WE Deutschland (Inland)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="10" t="inlineStr">
         <is>
           <t>DS</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -1194,68 +1194,68 @@
           <t>Lagerauftrag Werk DE – WE Frankreich (ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>FRxxx</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L10" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N10" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="O10" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -1268,68 +1268,68 @@
           <t>Strecke – Lieferant DE/EU (≠PL) – WE Polen</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>PLxxx</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" s="10" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1342,68 +1342,68 @@
           <t>Strecke – Lieferant DE/EU (≠CZ) – WE Tschechien</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr"/>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="9" t="inlineStr">
         <is>
           <t>CZxxx</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="10" t="inlineStr">
         <is>
           <t>AE</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="M12" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N12" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O12" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1416,68 +1416,68 @@
           <t>Strecke – Lieferant DE/EU (≠SI) – WE Slowenien</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="9" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L13" s="10" t="inlineStr">
         <is>
           <t>CB</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="N13" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1490,68 +1490,68 @@
           <t>Strecke – Lieferant Schweden – WE Slowenien</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>CB</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1564,68 +1564,68 @@
           <t>Strecke – Lieferant DE/EU (≠BE) – WE Belgien</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>BE1022245089</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>BExxx</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1638,48 +1638,48 @@
           <t>Strecke – Lieferant DE/EU (≠NL) – WE Niederlande</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>NL827914052B01</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
         <is>
           <t>NLxxx</t>
         </is>
@@ -1689,17 +1689,17 @@
           <t>⚠ kein SAP-Stkz (Lücke)</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="M16" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="N16" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="O16" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1712,68 +1712,68 @@
           <t>Strecke – Lieferant DE/EU (≠LV) – WE Lettland</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>LV90013367396</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>LVxxx</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L17" s="10" t="inlineStr">
         <is>
           <t>LS</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="N17" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1786,68 +1786,68 @@
           <t>Strecke – Lieferant DE/EU (≠EE) – WE Estland</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr"/>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>EE102839441</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>Ship-to</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>EE</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>EE</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>EExxx</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L18" s="10" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="N18" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="O18" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1860,68 +1860,68 @@
           <t>Strecke – Lieferant Slowenien – WE Ungarn (Dreieck)</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>HUxxx</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L19" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="M19" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="N19" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -1938,68 +1938,68 @@
           <t>Strecke – Lieferant Italien – WE Frankreich (Dreieck)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr"/>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>FRxxx</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L20" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
+      <c r="O20" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2016,68 +2016,68 @@
           <t>Strecke – Lieferant Polen – WE Spanien (Dreieck)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>ESxxx</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L21" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N21" s="3" t="inlineStr">
+      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2094,68 +2094,68 @@
           <t>Strecke – Lieferant Frankreich – WE Österreich (Dreieck)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>ATxxx</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L22" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="M22" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
+      <c r="N22" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
+      <c r="O22" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2172,68 +2172,68 @@
           <t>Strecke – Lieferant Tschechien – WE Rumänien (Dreieck)</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr"/>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>ROxxx</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L23" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="M23" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr">
+      <c r="N23" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2250,22 +2250,22 @@
           <t>Strecke EXW – Lieferant DE – WE Slowenien</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2275,47 +2275,47 @@
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L24" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M24" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr">
+      <c r="N24" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
+      <c r="O24" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2328,22 +2328,22 @@
           <t>Strecke EXW – Lieferant Slowenien (abgeholt) – WE Slowenien</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2353,47 +2353,47 @@
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L25" s="10" t="inlineStr">
         <is>
           <t>CB</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="M25" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N25" s="3" t="inlineStr">
+      <c r="N25" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="O25" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2406,22 +2406,22 @@
           <t>Strecke EXW – Lieferant Polen – WE Italien</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2431,47 +2431,47 @@
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>ITxxx</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="L26" s="10" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M26" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
+      <c r="N26" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
+      <c r="O26" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2484,22 +2484,22 @@
           <t>Strecke EXW – Lieferant Tschechien – WE Deutschland</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2509,47 +2509,47 @@
           <t>CZ687387072</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="L27" s="10" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="M27" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="N27" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="O27" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2562,22 +2562,22 @@
           <t>Strecke EXW – Lieferant Belgien – WE Belgien (Inland)</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2587,47 +2587,47 @@
           <t>BE1022245089</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>BExxx</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="L28" s="10" t="inlineStr">
         <is>
           <t>BS</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
+      <c r="M28" s="9" t="inlineStr">
         <is>
           <t>Inlandslieferung</t>
         </is>
       </c>
-      <c r="N28" s="3" t="inlineStr">
+      <c r="N28" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
+      <c r="O28" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2637,82 +2637,82 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Strecke EXW – Lieferant Italien (ohne EPDE-UID) – WE Slowenien</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
+          <t>Strecke EXW – Lieferant Italien (ohne EPDE-UID) – WE Slowenien (EPDE SI-registriert)</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>DE449663039</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>EXW: Lieferantland -&gt; BUKRS DE</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
+          <t>SI66423562</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>EXW: Lieferantland ohne EPDE-UID -&gt; Ship-to SI</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
         <is>
           <t>SIxxx</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>DH</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>ig. Lieferung</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>Inlandslieferung</t>
+        </is>
+      </c>
+      <c r="N29" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="O29" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>EXW: Lieferantland ohne EPDE-UID -&gt; BUKRS DE</t>
+          <t>EXW: Lieferantland IT, dort keine EPDE-UID -&gt; Fallback auf Ship-to-UID SI (NICHT BUKRS DE). Art. 36a Abs. 1: bewegte Lieferung ist die Eingangslieferung IT-&gt;EPDE, ig. Erwerb in SI (MIRO: EC). Dreieck Art. 141 lit. a gesperrt, weil eigene UID im Bestimmungsland vorhanden -&gt; L2 = SI-Inlandslieferung 22% (CB), kein DH. Vgl. EPROHA-Matrix "EXW – Lieferant IT – WE Slowenien": dort AF, weil EPROHA keine SI-Registrierung hat.</t>
         </is>
       </c>
     </row>
@@ -2722,22 +2722,22 @@
           <t>Strecke EXW – Lieferant Belgien – WE Frankreich (BE ig. Lief.)</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2747,27 +2747,27 @@
           <t>BE1022245089</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>FRxxx</t>
         </is>
@@ -2777,17 +2777,17 @@
           <t>⚠ kein SAP-Stkz (Lücke)</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N30" s="3" t="inlineStr">
+      <c r="N30" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
+      <c r="O30" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2800,22 +2800,22 @@
           <t>Strecke EXW – Lieferant Niederlande – WE Deutschland (NL ig. Lief.)</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -2825,27 +2825,27 @@
           <t>NL827914052B01</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
@@ -2855,17 +2855,17 @@
           <t>⚠ kein SAP-Stkz (Lücke)</t>
         </is>
       </c>
-      <c r="M31" s="3" t="inlineStr">
+      <c r="M31" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N31" s="3" t="inlineStr">
+      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
+      <c r="O31" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -2878,48 +2878,48 @@
           <t>Lagerauftrag Werk PL – WE Schweiz (Ausfuhr)</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr"/>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
         <is>
           <t>CHxxx</t>
         </is>
@@ -2929,17 +2929,17 @@
           <t>⚠ kein SAP-Stkz (Treatment fehlt: export)</t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="M32" s="9" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr">
+      <c r="N32" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
+      <c r="O32" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -2952,68 +2952,68 @@
           <t>Lager DE – WE Schweiz (Ausfuhr)</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr"/>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>CHxxx</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr">
+      <c r="L33" s="10" t="inlineStr">
         <is>
           <t>G0</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="M33" s="9" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
+      <c r="O33" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -3026,68 +3026,68 @@
           <t>Lager DE – WE Liechtenstein (Ausfuhr, Schweizer MWST-Raum)</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr"/>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>LI</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>LIxxx</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr">
+      <c r="L34" s="10" t="inlineStr">
         <is>
           <t>G0</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
+      <c r="M34" s="9" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N34" s="3" t="inlineStr">
+      <c r="N34" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
+      <c r="O34" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -3100,68 +3100,68 @@
           <t>Lager DE – WE Großbritannien (Ausfuhr, Post-Brexit)</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr"/>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>GBxxx</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="L35" s="10" t="inlineStr">
         <is>
           <t>G0</t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr">
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N35" s="3" t="inlineStr">
+      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
+      <c r="O35" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -3174,68 +3174,68 @@
           <t>Strecke – Lieferant DE/EU – WE Großbritannien (Ausfuhr)</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr"/>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K36" s="9" t="inlineStr">
         <is>
           <t>GBxxx</t>
         </is>
       </c>
-      <c r="L36" s="4" t="inlineStr">
+      <c r="L36" s="10" t="inlineStr">
         <is>
           <t>G0</t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr">
+      <c r="M36" s="9" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N36" s="3" t="inlineStr">
+      <c r="N36" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
+      <c r="O36" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -3252,48 +3252,48 @@
           <t>Lager PL-Werk – WE Großbritannien (Ausfuhr) [Lücke: kein PL-Export-Stkz]</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>1702</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr"/>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>PL5263841834</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>Werk</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K37" s="9" t="inlineStr">
         <is>
           <t>GBxxx</t>
         </is>
@@ -3303,17 +3303,17 @@
           <t>⚠ kein SAP-Stkz (Treatment fehlt: export)</t>
         </is>
       </c>
-      <c r="M37" s="3" t="inlineStr">
+      <c r="M37" s="9" t="inlineStr">
         <is>
           <t>Ausfuhr</t>
         </is>
       </c>
-      <c r="N37" s="3" t="inlineStr">
+      <c r="N37" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
+      <c r="O37" s="9" t="inlineStr">
         <is>
           <t>not relevant</t>
         </is>
@@ -3326,22 +3326,22 @@
           <t>Strecke EXW – Lieferant Slowenien – WE Italien (SI ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -3351,47 +3351,47 @@
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K38" s="9" t="inlineStr">
         <is>
           <t>ITxxx</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr">
+      <c r="L38" s="10" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr">
+      <c r="M38" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N38" s="3" t="inlineStr">
+      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
+      <c r="O38" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -3404,22 +3404,22 @@
           <t>Strecke EXW – Lieferant Slowenien – WE Deutschland (SI ig. Lieferung)</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>EXW</t>
         </is>
@@ -3429,47 +3429,47 @@
           <t>SI66423562</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>EXW: Lieferantland</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
         <is>
           <t>DExxx</t>
         </is>
       </c>
-      <c r="L39" s="4" t="inlineStr">
+      <c r="L39" s="10" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="M39" s="3" t="inlineStr">
+      <c r="M39" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N39" s="3" t="inlineStr">
+      <c r="N39" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
+      <c r="O39" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -3482,68 +3482,68 @@
           <t>Dreieck – Lieferant Frankreich → EPDE(DE) → WE Italien (Art. 141)</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr"/>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" s="9" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="K40" s="9" t="inlineStr">
         <is>
           <t>ITxxx</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="L40" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="M40" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N40" s="3" t="inlineStr">
+      <c r="N40" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
+      <c r="O40" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -3560,68 +3560,68 @@
           <t>Dreieck – Lieferant Italien → EPDE(DE) → WE Spanien (Art. 141)</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr"/>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
           <t>DE449663039</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>Ship-to -&gt; BUKRS DE</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" s="9" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
+      <c r="K41" s="9" t="inlineStr">
         <is>
           <t>ESxxx</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="L41" s="10" t="inlineStr">
         <is>
           <t>DH</t>
         </is>
       </c>
-      <c r="M41" s="3" t="inlineStr">
+      <c r="M41" s="9" t="inlineStr">
         <is>
           <t>ig. Lieferung</t>
         </is>
       </c>
-      <c r="N41" s="3" t="inlineStr">
+      <c r="N41" s="9" t="inlineStr">
         <is>
           <t>Unsere UID lautet: xxx</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
+      <c r="O41" s="9" t="inlineStr">
         <is>
           <t>⟶ in SAP prüfen</t>
         </is>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Sonderregel: dreht die maßgebliche eigene UID auf das LIEFERANTENLAND (überschreibt die Ship-to-Regel). Gleiche Warenkonstellation kann je Incoterm ein anderes Kennzeichen ergeben.</t>
+          <t>Sonderregel: dreht die maßgebliche eigene UID auf das LIEFERANTENLAND (überschreibt die Ship-to-Regel). Gleiche Warenkonstellation kann je Incoterm ein anderes Kennzeichen ergeben. FALLBACK: Hat EPDE im Lieferantenland KEINE UID (z. B. Italien), greift zuerst die Ship-to-UID (falls vorhanden), erst danach der Buchungskreis DE. Der frühere Direkt-Fallback auf BUKRS DE unterstellte ein Dreiecksgeschäft (DH), das nach Art. 141 lit. a gesperrt ist, sobald eine eigene UID im Bestimmungsland existiert (Beispiel EXW/IT -&gt; WE Slowenien: richtig ist SI-UID -&gt; CB, nicht DE-UID -&gt; DH).</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4828,6 +4828,53 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Lieferant IT → Ware nach SI (EXW-Abholung, Streckengeschäft)</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>EPDE</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>bewegt</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>SI66423562</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>ig. Erwerb (Selbstveranlagung)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>EXW: wir holen in IT ab, teilen SI-UID mit → L1 bewegt (Art. 36a Abs. 1) → ig. Erwerb SI (EC); Verkauf an SI-Kunden = SI-Inland 22% (CB)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
